--- a/server/api/offshore_forecast_api/models/topside_deck_feature_importance.xlsx
+++ b/server/api/offshore_forecast_api/models/topside_deck_feature_importance.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5194463729858398</v>
+        <v>0.5913284420967102</v>
       </c>
       <c r="C2" t="n">
-        <v>51.94463729858398</v>
+        <v>59.13284301757812</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4805535972118378</v>
+        <v>0.4086715281009674</v>
       </c>
       <c r="C3" t="n">
-        <v>48.05535888671875</v>
+        <v>40.86715316772461</v>
       </c>
     </row>
   </sheetData>
